--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0002T0006Z000C1N54_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0002T0006Z000C1N54_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>63.20139257761058</v>
+        <v>10.27022629386172</v>
       </c>
       <c r="D2" t="n">
-        <v>26.59652836721717</v>
+        <v>4.321935859672791</v>
       </c>
       <c r="E2" t="n">
-        <v>11.11320978616637</v>
+        <v>1.805896590252035</v>
       </c>
       <c r="F2" t="n">
-        <v>17.13911936518957</v>
+        <v>2.785106896843306</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>58.09150097649152</v>
+        <v>9.439868908679873</v>
       </c>
       <c r="D3" t="n">
-        <v>37.32842496144557</v>
+        <v>6.065869056234906</v>
       </c>
       <c r="E3" t="n">
-        <v>11.11320978616637</v>
+        <v>1.805896590252035</v>
       </c>
       <c r="F3" t="n">
-        <v>17.13911936518957</v>
+        <v>2.785106896843306</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>70.32231045670554</v>
+        <v>11.42737544921465</v>
       </c>
       <c r="D4" t="n">
-        <v>16.66366269224709</v>
+        <v>2.707845187490152</v>
       </c>
       <c r="E4" t="n">
-        <v>11.11320978616637</v>
+        <v>1.805896590252035</v>
       </c>
       <c r="F4" t="n">
-        <v>17.13911936518957</v>
+        <v>2.785106896843306</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>65.68015669705321</v>
+        <v>10.67302546327115</v>
       </c>
       <c r="D5" t="n">
-        <v>39.21950699800008</v>
+        <v>6.373169887175013</v>
       </c>
       <c r="E5" t="n">
-        <v>11.11320978616637</v>
+        <v>1.805896590252035</v>
       </c>
       <c r="F5" t="n">
-        <v>17.13911936518957</v>
+        <v>2.785106896843306</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>92.71759966626476</v>
+        <v>15.06660994576802</v>
       </c>
       <c r="D6" t="n">
-        <v>70.56057737367399</v>
+        <v>11.46609382322202</v>
       </c>
       <c r="E6" t="n">
-        <v>11.11320978616637</v>
+        <v>1.805896590252035</v>
       </c>
       <c r="F6" t="n">
-        <v>17.13911936518957</v>
+        <v>2.785106896843306</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>74.66730395486194</v>
+        <v>12.13343689266507</v>
       </c>
       <c r="D7" t="n">
-        <v>49.82699321628488</v>
+        <v>8.096886397646292</v>
       </c>
       <c r="E7" t="n">
-        <v>11.11320978616637</v>
+        <v>1.805896590252035</v>
       </c>
       <c r="F7" t="n">
-        <v>17.13911936518957</v>
+        <v>2.785106896843306</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
